--- a/Laboratorio/esperienza4/Esperienza4.xlsx
+++ b/Laboratorio/esperienza4/Esperienza4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michele/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alessiobrusini/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CC4755-5548-744F-A388-F103AAC7D106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:800001_{1F511E07-4B10-944B-AD32-1F3865122B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3620" yWindow="780" windowWidth="17120" windowHeight="19860" xr2:uid="{91E0D718-4DE5-43B7-A638-E0E64063323F}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{91E0D718-4DE5-43B7-A638-E0E64063323F}"/>
   </bookViews>
   <sheets>
     <sheet name="Parametri" sheetId="1" r:id="rId1"/>
@@ -73,6 +73,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -89,7 +92,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -99,6 +102,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -145,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -156,6 +165,11 @@
     </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -274,10 +288,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Dati!$A$2:$A$182</c:f>
+              <c:f>Dati!$A$2:$A$202</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="181"/>
+                <c:ptCount val="201"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -820,558 +834,672 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>362</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>364</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>366</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>368</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>372</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>374</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>376</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>378</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>382</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>384</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>386</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>388</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>392</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>394</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>396</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>398</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Dati!$C$2:$C$182</c:f>
+              <c:f>Dati!$C$2:$C$202</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="181"/>
+                <c:ptCount val="201"/>
                 <c:pt idx="0">
-                  <c:v>6.58</c:v>
+                  <c:v>4.82</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.55</c:v>
+                  <c:v>4.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.53</c:v>
+                  <c:v>4.7699999999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.49</c:v>
+                  <c:v>4.78</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.53</c:v>
+                  <c:v>4.74</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.5</c:v>
+                  <c:v>4.71</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.7</c:v>
+                  <c:v>4.68</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.67</c:v>
+                  <c:v>4.66</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.62</c:v>
+                  <c:v>4.62</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.56</c:v>
+                  <c:v>4.59</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.5</c:v>
+                  <c:v>4.5599999999999996</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6.44</c:v>
+                  <c:v>4.51</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6.37</c:v>
+                  <c:v>4.46</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.34</c:v>
+                  <c:v>4.4000000000000004</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6.25</c:v>
+                  <c:v>4.37</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>6.15</c:v>
+                  <c:v>4.32</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>6.08</c:v>
+                  <c:v>4.2300000000000004</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.98</c:v>
+                  <c:v>4.18</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.88</c:v>
+                  <c:v>4.0999999999999996</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.79</c:v>
+                  <c:v>4.01</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.68</c:v>
+                  <c:v>3.96</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.56</c:v>
+                  <c:v>3.88</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.48</c:v>
+                  <c:v>3.81</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.37</c:v>
+                  <c:v>3.74</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5.27</c:v>
+                  <c:v>3.68</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>5.16</c:v>
+                  <c:v>3.6</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>5.01</c:v>
+                  <c:v>3.54</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4.93</c:v>
+                  <c:v>3.47</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4.79</c:v>
+                  <c:v>3.41</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>3.37</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.29</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.22</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.16</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3.04</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2.99</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2.95</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2.86</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2.84</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2.79</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2.77</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2.76</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2.77</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2.77</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2.78</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2.79</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2.81</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2.83</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2.85</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2.92</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2.99</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>3.01</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>3.06</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>3.12</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>3.16</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>3.24</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>3.31</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>3.36</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>3.45</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>3.51</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>3.59</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>3.67</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>3.72</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>3.8</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>3.85</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>3.94</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>3.99</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>4.05</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>4.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>4.16</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>4.2300000000000004</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>4.28</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>4.3099999999999996</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>4.38</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>4.43</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>4.47</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>4.51</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>4.54</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>4.59</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>4.5999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>4.66</c:v>
+                </c:pt>
+                <c:pt idx="84">
                   <c:v>4.68</c:v>
                 </c:pt>
-                <c:pt idx="30">
-                  <c:v>4.54</c:v>
-                </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="85">
+                  <c:v>4.6900000000000004</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>4.71</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4.72</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>4.7300000000000004</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>4.74</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>4.72</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>4.7300000000000004</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>4.74</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>4.72</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>4.72</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>4.6500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>4.62</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4.58</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>4.57</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>4.51</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>4.46</c:v>
+                </c:pt>
+                <c:pt idx="102">
                   <c:v>4.4400000000000004</c:v>
                 </c:pt>
-                <c:pt idx="32">
-                  <c:v>4.33</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>4.22</c:v>
-                </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="103">
+                  <c:v>4.38</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>4.34</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>4.26</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>4.12</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>4.08</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>3.92</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>3.86</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>3.8</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>3.73</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>3.67</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>3.58</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>3.53</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>3.48</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>3.38</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>3.33</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>3.26</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>3.18</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>3.15</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>3.06</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>3.03</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>2.98</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>2.92</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>2.88</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>2.85</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>2.82</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>2.79</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>2.79</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>2.77</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>2.75</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>2.75</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>2.76</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>2.77</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>2.79</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>2.81</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>2.86</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>2.87</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>2.88</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>2.94</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>2.98</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>3.01</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>3.06</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>3.13</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>3.18</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>3.24</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>3.31</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>3.35</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>3.42</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>3.49</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>3.57</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>3.62</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>3.69</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>3.78</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>3.82</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>3.88</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>3.95</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>3.99</c:v>
+                </c:pt>
+                <c:pt idx="161">
                   <c:v>4.0599999999999996</c:v>
                 </c:pt>
-                <c:pt idx="35">
-                  <c:v>3.99</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>3.94</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>3.87</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>3.8</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>3.73</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>3.69</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>3.61</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>3.57</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>3.56</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>3.53</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>3.53</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>3.53</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>3.45</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>3.47</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>3.49</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>3.53</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>3.61</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>3.65</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>3.72</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>3.75</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>3.78</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>3.88</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>3.98</c:v>
-                </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="162">
+                  <c:v>4.12</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>4.21</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>4.26</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>4.32</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>4.3600000000000003</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>4.41</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>4.47</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>4.49</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>4.53</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>4.58</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>4.6100000000000003</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>4.62</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>4.6500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>4.66</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>4.72</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>4.74</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>4.72</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>4.72</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>4.72</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>4.71</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>4.6900000000000004</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>4.68</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>4.6399999999999997</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>4.6100000000000003</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>4.58</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>4.5599999999999996</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>4.5199999999999996</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>4.46</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>4.42</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>4.37</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>4.32</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>4.26</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>4.1500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>4.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="199">
                   <c:v>4.05</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>4.1500000000000004</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>4.28</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>4.41</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>4.4800000000000004</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>4.57</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>4.7</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>4.8</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>4.95</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>5.05</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>5.14</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>5.27</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>5.33</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>5.41</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>5.51</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>5.63</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>5.69</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>5.75</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>5.83</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>5.9</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>6.03</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>6.09</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>6.13</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>6.2</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>6.24</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>6.29</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>6.31</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>6.33</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>6.35</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>6.38</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>6.38</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>6.38</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>6.37</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>6.36</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>6.35</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>6.33</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>6.3</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>6.2</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>6.22</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>6.23</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>6.16</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>6.11</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>6.06</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>5.96</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>5.9</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>5.81</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>5.73</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>5.65</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>5.57</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>5.49</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>5.4</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>5.3</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>5.22</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>5.13</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>5.03</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>4.88</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>4.79</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>4.7</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>4.58</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>4.51</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>4.4000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>4.29</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>4.18</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>4.08</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>3.9</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>3.83</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>3.74</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>3.69</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>3.61</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>3.56</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>3.51</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>3.48</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>3.42</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>3.39</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>3.38</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>3.35</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>3.35</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>3.35</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>3.37</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>3.37</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>3.41</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>3.45</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>3.48</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>3.57</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>3.63</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>3.7</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>3.77</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>3.84</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>3.89</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>4.09</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>4.2</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>4.33</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>4.4400000000000004</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>4.4800000000000004</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>4.5999999999999996</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>4.71</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>4.8</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>4.92</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>5.1100000000000003</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>5.24</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>5.32</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>5.42</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>5.53</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>5.62</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>5.69</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>5.78</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>5.83</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>5.92</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>5.97</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>6.01</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>6.09</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>6.11</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>6.18</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>6.22</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>6.28</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>6.3</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>6.35</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>6.38</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>6.38</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>6.38</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2516,11 +2644,11 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <f>0.5</f>
-        <v>0.5</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>5.7735030000000001E-3</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -2531,7 +2659,7 @@
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f>A2*PI()/180</f>
-        <v>8.7266462599716477E-3</v>
+        <v>1.7453292519943295E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2541,12 +2669,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF341A33-A13A-4046-A547-8DE2389C519B}">
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:F201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="4"/>
-    <col min="2" max="2" width="5.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="8.83203125" style="4"/>
+    <col min="1" max="4" width="8.83203125" style="4"/>
+    <col min="5" max="5" width="8.83203125" style="8"/>
     <col min="6" max="6" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="8.83203125" style="5"/>
   </cols>
@@ -2564,7 +2691,7 @@
       <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -2581,15 +2708,15 @@
         <v>0</v>
       </c>
       <c r="C2" s="4">
-        <v>6.58</v>
+        <v>4.82</v>
       </c>
       <c r="D2" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E2" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E2" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -2602,15 +2729,15 @@
         <v>3.4906585039886591E-2</v>
       </c>
       <c r="C3" s="4">
-        <v>6.55</v>
+        <v>4.8</v>
       </c>
       <c r="D3" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E3" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E3" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2623,15 +2750,15 @@
         <v>6.9813170079773182E-2</v>
       </c>
       <c r="C4" s="4">
-        <v>6.53</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="D4" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E4" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E4" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2644,15 +2771,15 @@
         <v>0.10471975511965977</v>
       </c>
       <c r="C5" s="4">
-        <v>6.49</v>
+        <v>4.78</v>
       </c>
       <c r="D5" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E5" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E5" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -2665,15 +2792,15 @@
         <v>0.13962634015954636</v>
       </c>
       <c r="C6" s="4">
-        <v>6.53</v>
+        <v>4.74</v>
       </c>
       <c r="D6" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E6" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E6" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -2686,15 +2813,15 @@
         <v>0.17453292519943295</v>
       </c>
       <c r="C7" s="4">
-        <v>6.5</v>
+        <v>4.71</v>
       </c>
       <c r="D7" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E7" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E7" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -2707,15 +2834,15 @@
         <v>0.20943951023931953</v>
       </c>
       <c r="C8" s="4">
-        <v>6.7</v>
+        <v>4.68</v>
       </c>
       <c r="D8" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E8" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E8" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -2728,15 +2855,15 @@
         <v>0.24434609527920614</v>
       </c>
       <c r="C9" s="4">
-        <v>6.67</v>
+        <v>4.66</v>
       </c>
       <c r="D9" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E9" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E9" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -2749,15 +2876,15 @@
         <v>0.27925268031909273</v>
       </c>
       <c r="C10" s="4">
-        <v>6.62</v>
+        <v>4.62</v>
       </c>
       <c r="D10" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E10" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E10" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -2770,15 +2897,15 @@
         <v>0.31415926535897931</v>
       </c>
       <c r="C11" s="4">
-        <v>6.56</v>
+        <v>4.59</v>
       </c>
       <c r="D11" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E11" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E11" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -2791,15 +2918,15 @@
         <v>0.3490658503988659</v>
       </c>
       <c r="C12" s="4">
-        <v>6.5</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="D12" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E12" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E12" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -2812,15 +2939,15 @@
         <v>0.38397243543875248</v>
       </c>
       <c r="C13" s="4">
-        <v>6.44</v>
+        <v>4.51</v>
       </c>
       <c r="D13" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E13" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E13" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -2833,15 +2960,15 @@
         <v>0.41887902047863906</v>
       </c>
       <c r="C14" s="4">
-        <v>6.37</v>
+        <v>4.46</v>
       </c>
       <c r="D14" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E14" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E14" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -2854,15 +2981,15 @@
         <v>0.4537856055185257</v>
       </c>
       <c r="C15" s="4">
-        <v>6.34</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="D15" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E15" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E15" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -2875,15 +3002,15 @@
         <v>0.48869219055841229</v>
       </c>
       <c r="C16" s="4">
-        <v>6.25</v>
+        <v>4.37</v>
       </c>
       <c r="D16" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E16" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E16" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -2896,15 +3023,15 @@
         <v>0.52359877559829882</v>
       </c>
       <c r="C17" s="4">
-        <v>6.15</v>
+        <v>4.32</v>
       </c>
       <c r="D17" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E17" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E17" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -2917,15 +3044,15 @@
         <v>0.55850536063818546</v>
       </c>
       <c r="C18" s="4">
-        <v>6.08</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="D18" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E18" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E18" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -2938,15 +3065,15 @@
         <v>0.59341194567807209</v>
       </c>
       <c r="C19" s="4">
-        <v>5.98</v>
+        <v>4.18</v>
       </c>
       <c r="D19" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E19" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E19" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -2959,15 +3086,15 @@
         <v>0.62831853071795862</v>
       </c>
       <c r="C20" s="4">
-        <v>5.88</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D20" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E20" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E20" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -2980,15 +3107,15 @@
         <v>0.66322511575784515</v>
       </c>
       <c r="C21" s="4">
-        <v>5.79</v>
+        <v>4.01</v>
       </c>
       <c r="D21" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E21" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E21" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -3001,15 +3128,15 @@
         <v>0.69813170079773179</v>
       </c>
       <c r="C22" s="4">
-        <v>5.68</v>
+        <v>3.96</v>
       </c>
       <c r="D22" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E22" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E22" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -3022,15 +3149,15 @@
         <v>0.73303828583761843</v>
       </c>
       <c r="C23" s="4">
-        <v>5.56</v>
+        <v>3.88</v>
       </c>
       <c r="D23" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E23" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E23" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -3043,15 +3170,15 @@
         <v>0.76794487087750496</v>
       </c>
       <c r="C24" s="4">
-        <v>5.48</v>
+        <v>3.81</v>
       </c>
       <c r="D24" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E24" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E24" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -3064,15 +3191,15 @@
         <v>0.80285145591739149</v>
       </c>
       <c r="C25" s="4">
-        <v>5.37</v>
+        <v>3.74</v>
       </c>
       <c r="D25" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E25" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E25" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -3085,15 +3212,15 @@
         <v>0.83775804095727813</v>
       </c>
       <c r="C26" s="4">
-        <v>5.27</v>
+        <v>3.68</v>
       </c>
       <c r="D26" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E26" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E26" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -3106,15 +3233,15 @@
         <v>0.87266462599716477</v>
       </c>
       <c r="C27" s="4">
-        <v>5.16</v>
+        <v>3.6</v>
       </c>
       <c r="D27" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E27" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E27" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -3127,15 +3254,15 @@
         <v>0.90757121103705141</v>
       </c>
       <c r="C28" s="4">
-        <v>5.01</v>
+        <v>3.54</v>
       </c>
       <c r="D28" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E28" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E28" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -3148,15 +3275,15 @@
         <v>0.94247779607693793</v>
       </c>
       <c r="C29" s="4">
-        <v>4.93</v>
+        <v>3.47</v>
       </c>
       <c r="D29" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E29" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E29" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -3169,15 +3296,15 @@
         <v>0.97738438111682457</v>
       </c>
       <c r="C30" s="4">
-        <v>4.79</v>
+        <v>3.41</v>
       </c>
       <c r="D30" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E30" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E30" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -3190,15 +3317,15 @@
         <v>1.0122909661567112</v>
       </c>
       <c r="C31" s="4">
-        <v>4.68</v>
+        <v>3.37</v>
       </c>
       <c r="D31" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E31" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E31" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -3211,15 +3338,15 @@
         <v>1.0471975511965976</v>
       </c>
       <c r="C32" s="4">
-        <v>4.54</v>
+        <v>3.29</v>
       </c>
       <c r="D32" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E32" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E32" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -3232,15 +3359,15 @@
         <v>1.0821041362364843</v>
       </c>
       <c r="C33" s="4">
-        <v>4.4400000000000004</v>
+        <v>3.22</v>
       </c>
       <c r="D33" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E33" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E33" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -3253,15 +3380,15 @@
         <v>1.1170107212763709</v>
       </c>
       <c r="C34" s="4">
-        <v>4.33</v>
+        <v>3.16</v>
       </c>
       <c r="D34" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E34" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E34" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -3274,15 +3401,15 @@
         <v>1.1519173063162575</v>
       </c>
       <c r="C35" s="4">
-        <v>4.22</v>
+        <v>3.1</v>
       </c>
       <c r="D35" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E35" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E35" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -3295,15 +3422,15 @@
         <v>1.1868238913561442</v>
       </c>
       <c r="C36" s="4">
-        <v>4.0599999999999996</v>
+        <v>3.04</v>
       </c>
       <c r="D36" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E36" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E36" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -3316,15 +3443,15 @@
         <v>1.2217304763960306</v>
       </c>
       <c r="C37" s="4">
-        <v>3.99</v>
+        <v>2.99</v>
       </c>
       <c r="D37" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E37" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E37" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -3337,15 +3464,15 @@
         <v>1.2566370614359172</v>
       </c>
       <c r="C38" s="4">
-        <v>3.94</v>
+        <v>2.95</v>
       </c>
       <c r="D38" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E38" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E38" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -3358,15 +3485,15 @@
         <v>1.2915436464758039</v>
       </c>
       <c r="C39" s="4">
-        <v>3.87</v>
+        <v>2.9</v>
       </c>
       <c r="D39" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E39" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E39" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -3379,15 +3506,15 @@
         <v>1.3264502315156903</v>
       </c>
       <c r="C40" s="4">
-        <v>3.8</v>
+        <v>2.86</v>
       </c>
       <c r="D40" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E40" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E40" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -3400,15 +3527,15 @@
         <v>1.3613568165555769</v>
       </c>
       <c r="C41" s="4">
-        <v>3.73</v>
+        <v>2.84</v>
       </c>
       <c r="D41" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E41" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E41" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -3421,15 +3548,15 @@
         <v>1.3962634015954636</v>
       </c>
       <c r="C42" s="4">
-        <v>3.69</v>
+        <v>2.8</v>
       </c>
       <c r="D42" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E42" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E42" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -3442,15 +3569,15 @@
         <v>1.43116998663535</v>
       </c>
       <c r="C43" s="4">
-        <v>3.61</v>
+        <v>2.79</v>
       </c>
       <c r="D43" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E43" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E43" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -3463,15 +3590,15 @@
         <v>1.4660765716752369</v>
       </c>
       <c r="C44" s="4">
-        <v>3.57</v>
+        <v>2.77</v>
       </c>
       <c r="D44" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E44" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E44" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -3484,15 +3611,15 @@
         <v>1.5009831567151233</v>
       </c>
       <c r="C45" s="4">
-        <v>3.56</v>
+        <v>2.76</v>
       </c>
       <c r="D45" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E45" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E45" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -3505,15 +3632,15 @@
         <v>1.5358897417550099</v>
       </c>
       <c r="C46" s="4">
-        <v>3.53</v>
+        <v>2.77</v>
       </c>
       <c r="D46" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E46" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E46" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -3526,15 +3653,15 @@
         <v>1.5707963267948966</v>
       </c>
       <c r="C47" s="4">
-        <v>3.53</v>
+        <v>2.77</v>
       </c>
       <c r="D47" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E47" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E47" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -3547,18 +3674,18 @@
         <v>1.605702911834783</v>
       </c>
       <c r="C48" s="4">
-        <v>3.53</v>
+        <v>2.78</v>
       </c>
       <c r="D48" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E48" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E48" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -3568,18 +3695,18 @@
         <v>1.6406094968746698</v>
       </c>
       <c r="C49" s="4">
-        <v>3.45</v>
+        <v>2.79</v>
       </c>
       <c r="D49" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E49" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E49" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -3589,18 +3716,18 @@
         <v>1.6755160819145563</v>
       </c>
       <c r="C50" s="4">
-        <v>3.47</v>
+        <v>2.81</v>
       </c>
       <c r="D50" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E50" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E50" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -3610,18 +3737,18 @@
         <v>1.7104226669544429</v>
       </c>
       <c r="C51" s="4">
-        <v>3.49</v>
+        <v>2.83</v>
       </c>
       <c r="D51" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E51" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E51" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -3631,18 +3758,18 @@
         <v>1.7453292519943295</v>
       </c>
       <c r="C52" s="4">
-        <v>3.53</v>
+        <v>2.85</v>
       </c>
       <c r="D52" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E52" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E52" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -3652,18 +3779,18 @@
         <v>1.780235837034216</v>
       </c>
       <c r="C53" s="4">
-        <v>3.61</v>
+        <v>2.9</v>
       </c>
       <c r="D53" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E53" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E53" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -3673,18 +3800,18 @@
         <v>1.8151424220741028</v>
       </c>
       <c r="C54" s="4">
-        <v>3.65</v>
+        <v>2.92</v>
       </c>
       <c r="D54" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E54" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E54" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -3694,18 +3821,18 @@
         <v>1.8500490071139892</v>
       </c>
       <c r="C55" s="4">
-        <v>3.72</v>
+        <v>2.99</v>
       </c>
       <c r="D55" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E55" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E55" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -3715,18 +3842,18 @@
         <v>1.8849555921538759</v>
       </c>
       <c r="C56" s="4">
-        <v>3.75</v>
+        <v>3.01</v>
       </c>
       <c r="D56" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E56" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E56" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -3736,18 +3863,18 @@
         <v>1.9198621771937625</v>
       </c>
       <c r="C57" s="4">
-        <v>3.78</v>
+        <v>3.06</v>
       </c>
       <c r="D57" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E57" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E57" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -3757,18 +3884,18 @@
         <v>1.9547687622336491</v>
       </c>
       <c r="C58" s="4">
-        <v>3.88</v>
+        <v>3.12</v>
       </c>
       <c r="D58" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E58" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E58" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -3778,18 +3905,19 @@
         <v>1.9896753472735356</v>
       </c>
       <c r="C59" s="4">
-        <v>3.98</v>
+        <v>3.16</v>
       </c>
       <c r="D59" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E59" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E59" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+      <c r="F59" s="6"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <f t="shared" si="1"/>
         <v>116</v>
@@ -3799,18 +3927,18 @@
         <v>2.0245819323134224</v>
       </c>
       <c r="C60" s="4">
-        <v>4.05</v>
+        <v>3.24</v>
       </c>
       <c r="D60" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E60" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E60" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <f t="shared" si="1"/>
         <v>118</v>
@@ -3820,18 +3948,18 @@
         <v>2.0594885173533086</v>
       </c>
       <c r="C61" s="4">
-        <v>4.1500000000000004</v>
+        <v>3.31</v>
       </c>
       <c r="D61" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E61" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E61" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -3841,18 +3969,18 @@
         <v>2.0943951023931953</v>
       </c>
       <c r="C62" s="4">
-        <v>4.28</v>
+        <v>3.36</v>
       </c>
       <c r="D62" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E62" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E62" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <f t="shared" si="1"/>
         <v>122</v>
@@ -3862,18 +3990,18 @@
         <v>2.1293016874330819</v>
       </c>
       <c r="C63" s="4">
-        <v>4.41</v>
+        <v>3.45</v>
       </c>
       <c r="D63" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E63" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E63" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <f t="shared" si="1"/>
         <v>124</v>
@@ -3883,15 +4011,15 @@
         <v>2.1642082724729685</v>
       </c>
       <c r="C64" s="4">
-        <v>4.4800000000000004</v>
+        <v>3.51</v>
       </c>
       <c r="D64" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E64" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E64" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -3904,15 +4032,15 @@
         <v>2.1991148575128552</v>
       </c>
       <c r="C65" s="4">
-        <v>4.57</v>
+        <v>3.59</v>
       </c>
       <c r="D65" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E65" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E65" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -3925,15 +4053,15 @@
         <v>2.2340214425527418</v>
       </c>
       <c r="C66" s="4">
-        <v>4.7</v>
+        <v>3.67</v>
       </c>
       <c r="D66" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E66" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E66" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -3946,15 +4074,15 @@
         <v>2.2689280275926285</v>
       </c>
       <c r="C67" s="4">
-        <v>4.8</v>
+        <v>3.72</v>
       </c>
       <c r="D67" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E67" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E67" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -3967,15 +4095,15 @@
         <v>2.3038346126325151</v>
       </c>
       <c r="C68" s="4">
-        <v>4.95</v>
+        <v>3.8</v>
       </c>
       <c r="D68" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E68" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E68" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -3988,15 +4116,15 @@
         <v>2.3387411976724013</v>
       </c>
       <c r="C69" s="4">
-        <v>5.05</v>
+        <v>3.85</v>
       </c>
       <c r="D69" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E69" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E69" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
@@ -4009,15 +4137,15 @@
         <v>2.3736477827122884</v>
       </c>
       <c r="C70" s="4">
-        <v>5.14</v>
+        <v>3.94</v>
       </c>
       <c r="D70" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E70" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E70" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
@@ -4030,15 +4158,15 @@
         <v>2.4085543677521746</v>
       </c>
       <c r="C71" s="4">
-        <v>5.27</v>
+        <v>3.99</v>
       </c>
       <c r="D71" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E71" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E71" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
@@ -4051,15 +4179,15 @@
         <v>2.4434609527920612</v>
       </c>
       <c r="C72" s="4">
-        <v>5.33</v>
+        <v>4.05</v>
       </c>
       <c r="D72" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E72" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E72" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
@@ -4072,15 +4200,15 @@
         <v>2.4783675378319479</v>
       </c>
       <c r="C73" s="4">
-        <v>5.41</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D73" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E73" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E73" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
@@ -4093,15 +4221,15 @@
         <v>2.5132741228718345</v>
       </c>
       <c r="C74" s="4">
-        <v>5.51</v>
+        <v>4.16</v>
       </c>
       <c r="D74" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E74" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E74" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
@@ -4114,15 +4242,15 @@
         <v>2.5481807079117211</v>
       </c>
       <c r="C75" s="4">
-        <v>5.63</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="D75" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E75" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E75" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
@@ -4135,15 +4263,15 @@
         <v>2.5830872929516078</v>
       </c>
       <c r="C76" s="4">
-        <v>5.69</v>
+        <v>4.28</v>
       </c>
       <c r="D76" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E76" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E76" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
@@ -4156,15 +4284,15 @@
         <v>2.6179938779914944</v>
       </c>
       <c r="C77" s="4">
-        <v>5.75</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="D77" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E77" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E77" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
@@ -4177,15 +4305,15 @@
         <v>2.6529004630313806</v>
       </c>
       <c r="C78" s="4">
-        <v>5.83</v>
+        <v>4.38</v>
       </c>
       <c r="D78" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E78" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E78" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
@@ -4198,15 +4326,15 @@
         <v>2.6878070480712677</v>
       </c>
       <c r="C79" s="4">
-        <v>5.9</v>
+        <v>4.43</v>
       </c>
       <c r="D79" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E79" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E79" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
@@ -4219,15 +4347,15 @@
         <v>2.7227136331111539</v>
       </c>
       <c r="C80" s="4">
-        <v>6.03</v>
+        <v>4.47</v>
       </c>
       <c r="D80" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E80" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E80" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
@@ -4240,15 +4368,15 @@
         <v>2.7576202181510405</v>
       </c>
       <c r="C81" s="4">
-        <v>6.09</v>
+        <v>4.51</v>
       </c>
       <c r="D81" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E81" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E81" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
@@ -4261,15 +4389,15 @@
         <v>2.7925268031909272</v>
       </c>
       <c r="C82" s="4">
-        <v>6.13</v>
+        <v>4.54</v>
       </c>
       <c r="D82" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E82" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E82" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
@@ -4282,15 +4410,15 @@
         <v>2.8274333882308138</v>
       </c>
       <c r="C83" s="4">
-        <v>6.2</v>
+        <v>4.59</v>
       </c>
       <c r="D83" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E83" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E83" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
@@ -4303,15 +4431,15 @@
         <v>2.8623399732707</v>
       </c>
       <c r="C84" s="4">
-        <v>6.24</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D84" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E84" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E84" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
@@ -4324,15 +4452,15 @@
         <v>2.8972465583105871</v>
       </c>
       <c r="C85" s="4">
-        <v>6.29</v>
+        <v>4.66</v>
       </c>
       <c r="D85" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E85" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E85" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
@@ -4345,15 +4473,15 @@
         <v>2.9321531433504737</v>
       </c>
       <c r="C86" s="4">
-        <v>6.31</v>
+        <v>4.68</v>
       </c>
       <c r="D86" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E86" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E86" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
@@ -4366,15 +4494,15 @@
         <v>2.9670597283903604</v>
       </c>
       <c r="C87" s="4">
-        <v>6.33</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="D87" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E87" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E87" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
@@ -4387,15 +4515,15 @@
         <v>3.0019663134302466</v>
       </c>
       <c r="C88" s="4">
-        <v>6.35</v>
+        <v>4.71</v>
       </c>
       <c r="D88" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E88" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E88" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
@@ -4408,15 +4536,15 @@
         <v>3.0368728984701332</v>
       </c>
       <c r="C89" s="4">
-        <v>6.38</v>
+        <v>4.72</v>
       </c>
       <c r="D89" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E89" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E89" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
@@ -4429,15 +4557,15 @@
         <v>3.0717794835100198</v>
       </c>
       <c r="C90" s="4">
-        <v>6.38</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="D90" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E90" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E90" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
@@ -4450,15 +4578,15 @@
         <v>3.1066860685499069</v>
       </c>
       <c r="C91" s="4">
-        <v>6.38</v>
+        <v>4.74</v>
       </c>
       <c r="D91" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E91" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E91" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
@@ -4471,15 +4599,15 @@
         <v>3.1415926535897931</v>
       </c>
       <c r="C92" s="4">
-        <v>6.37</v>
+        <v>4.72</v>
       </c>
       <c r="D92" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E92" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E92" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
@@ -4492,15 +4620,15 @@
         <v>3.1764992386296798</v>
       </c>
       <c r="C93" s="4">
-        <v>6.36</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="D93" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E93" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E93" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
@@ -4513,15 +4641,15 @@
         <v>3.211405823669566</v>
       </c>
       <c r="C94" s="4">
-        <v>6.35</v>
+        <v>4.74</v>
       </c>
       <c r="D94" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E94" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E94" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
@@ -4534,15 +4662,15 @@
         <v>3.2463124087094526</v>
       </c>
       <c r="C95" s="4">
-        <v>6.33</v>
+        <v>4.72</v>
       </c>
       <c r="D95" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E95" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E95" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
@@ -4555,15 +4683,15 @@
         <v>3.2812189937493397</v>
       </c>
       <c r="C96" s="4">
-        <v>6.3</v>
+        <v>4.72</v>
       </c>
       <c r="D96" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E96" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E96" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
@@ -4576,15 +4704,15 @@
         <v>3.3161255787892263</v>
       </c>
       <c r="C97" s="4">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="D97" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E97" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E97" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
@@ -4597,15 +4725,15 @@
         <v>3.3510321638291125</v>
       </c>
       <c r="C98" s="4">
-        <v>6.22</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="D98" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E98" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E98" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
@@ -4618,15 +4746,15 @@
         <v>3.3859387488689991</v>
       </c>
       <c r="C99" s="4">
-        <v>6.23</v>
+        <v>4.62</v>
       </c>
       <c r="D99" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E99" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E99" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
@@ -4639,15 +4767,15 @@
         <v>3.4208453339088858</v>
       </c>
       <c r="C100" s="4">
-        <v>6.16</v>
+        <v>4.58</v>
       </c>
       <c r="D100" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E100" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E100" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
@@ -4660,15 +4788,15 @@
         <v>3.4557519189487729</v>
       </c>
       <c r="C101" s="4">
-        <v>6.11</v>
+        <v>4.57</v>
       </c>
       <c r="D101" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E101" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E101" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
@@ -4681,15 +4809,15 @@
         <v>3.4906585039886591</v>
       </c>
       <c r="C102" s="4">
-        <v>6.06</v>
+        <v>4.51</v>
       </c>
       <c r="D102" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E102" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E102" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
@@ -4702,15 +4830,15 @@
         <v>3.5255650890285457</v>
       </c>
       <c r="C103" s="4">
-        <v>5.96</v>
+        <v>4.46</v>
       </c>
       <c r="D103" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E103" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E103" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
@@ -4723,15 +4851,15 @@
         <v>3.5604716740684319</v>
       </c>
       <c r="C104" s="4">
-        <v>5.9</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="D104" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E104" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E104" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
@@ -4744,15 +4872,15 @@
         <v>3.5953782591083185</v>
       </c>
       <c r="C105" s="4">
-        <v>5.81</v>
+        <v>4.38</v>
       </c>
       <c r="D105" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E105" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E105" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
@@ -4765,15 +4893,15 @@
         <v>3.6302848441482056</v>
       </c>
       <c r="C106" s="4">
-        <v>5.73</v>
+        <v>4.34</v>
       </c>
       <c r="D106" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E106" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E106" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
@@ -4786,15 +4914,15 @@
         <v>3.6651914291880923</v>
       </c>
       <c r="C107" s="4">
-        <v>5.65</v>
+        <v>4.26</v>
       </c>
       <c r="D107" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E107" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E107" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
@@ -4807,15 +4935,15 @@
         <v>3.7000980142279785</v>
       </c>
       <c r="C108" s="4">
-        <v>5.57</v>
+        <v>4.2</v>
       </c>
       <c r="D108" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E108" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E108" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
@@ -4828,15 +4956,15 @@
         <v>3.7350045992678651</v>
       </c>
       <c r="C109" s="4">
-        <v>5.49</v>
+        <v>4.12</v>
       </c>
       <c r="D109" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E109" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E109" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
@@ -4849,15 +4977,15 @@
         <v>3.7699111843077517</v>
       </c>
       <c r="C110" s="4">
-        <v>5.4</v>
+        <v>4.08</v>
       </c>
       <c r="D110" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E110" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E110" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
@@ -4870,15 +4998,15 @@
         <v>3.8048177693476379</v>
       </c>
       <c r="C111" s="4">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="D111" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E111" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E111" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
@@ -4891,15 +5019,15 @@
         <v>3.839724354387525</v>
       </c>
       <c r="C112" s="4">
-        <v>5.22</v>
+        <v>3.92</v>
       </c>
       <c r="D112" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E112" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E112" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
@@ -4912,15 +5040,15 @@
         <v>3.8746309394274117</v>
       </c>
       <c r="C113" s="4">
-        <v>5.13</v>
+        <v>3.86</v>
       </c>
       <c r="D113" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E113" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E113" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
@@ -4933,15 +5061,15 @@
         <v>3.9095375244672983</v>
       </c>
       <c r="C114" s="4">
-        <v>5.03</v>
+        <v>3.8</v>
       </c>
       <c r="D114" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E114" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E114" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
@@ -4954,15 +5082,15 @@
         <v>3.9444441095071845</v>
       </c>
       <c r="C115" s="4">
-        <v>4.88</v>
+        <v>3.73</v>
       </c>
       <c r="D115" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E115" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E115" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
@@ -4975,15 +5103,15 @@
         <v>3.9793506945470711</v>
       </c>
       <c r="C116" s="4">
-        <v>4.79</v>
+        <v>3.67</v>
       </c>
       <c r="D116" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E116" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E116" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
@@ -4996,15 +5124,15 @@
         <v>4.0142572795869578</v>
       </c>
       <c r="C117" s="4">
-        <v>4.7</v>
+        <v>3.58</v>
       </c>
       <c r="D117" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E117" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E117" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
@@ -5017,15 +5145,15 @@
         <v>4.0491638646268449</v>
       </c>
       <c r="C118" s="4">
-        <v>4.58</v>
+        <v>3.53</v>
       </c>
       <c r="D118" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E118" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E118" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
@@ -5038,15 +5166,15 @@
         <v>4.0840704496667311</v>
       </c>
       <c r="C119" s="4">
-        <v>4.51</v>
+        <v>3.48</v>
       </c>
       <c r="D119" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E119" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E119" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
@@ -5059,15 +5187,15 @@
         <v>4.1189770347066172</v>
       </c>
       <c r="C120" s="4">
-        <v>4.4000000000000004</v>
+        <v>3.38</v>
       </c>
       <c r="D120" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E120" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E120" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
@@ -5080,15 +5208,15 @@
         <v>4.1538836197465043</v>
       </c>
       <c r="C121" s="4">
-        <v>4.29</v>
+        <v>3.33</v>
       </c>
       <c r="D121" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E121" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E121" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
@@ -5101,15 +5229,15 @@
         <v>4.1887902047863905</v>
       </c>
       <c r="C122" s="4">
-        <v>4.18</v>
+        <v>3.26</v>
       </c>
       <c r="D122" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E122" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E122" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
@@ -5122,15 +5250,15 @@
         <v>4.2236967898262776</v>
       </c>
       <c r="C123" s="4">
-        <v>4.08</v>
+        <v>3.18</v>
       </c>
       <c r="D123" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E123" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E123" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
@@ -5143,15 +5271,15 @@
         <v>4.2586033748661638</v>
       </c>
       <c r="C124" s="4">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="D124" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E124" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E124" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
@@ -5164,15 +5292,15 @@
         <v>4.2935099599060509</v>
       </c>
       <c r="C125" s="4">
-        <v>3.9</v>
+        <v>3.06</v>
       </c>
       <c r="D125" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E125" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E125" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
@@ -5185,15 +5313,15 @@
         <v>4.3284165449459371</v>
       </c>
       <c r="C126" s="4">
-        <v>3.83</v>
+        <v>3.03</v>
       </c>
       <c r="D126" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E126" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E126" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
@@ -5206,15 +5334,15 @@
         <v>4.3633231299858233</v>
       </c>
       <c r="C127" s="4">
-        <v>3.74</v>
+        <v>2.98</v>
       </c>
       <c r="D127" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E127" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E127" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
@@ -5227,18 +5355,18 @@
         <v>4.3982297150257104</v>
       </c>
       <c r="C128" s="4">
-        <v>3.69</v>
+        <v>2.92</v>
       </c>
       <c r="D128" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E128" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E128" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="4">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -5248,18 +5376,18 @@
         <v>4.4331363000655974</v>
       </c>
       <c r="C129" s="4">
-        <v>3.61</v>
+        <v>2.88</v>
       </c>
       <c r="D129" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E129" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E129" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="4">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -5269,39 +5397,39 @@
         <v>4.4680428851054836</v>
       </c>
       <c r="C130" s="4">
-        <v>3.56</v>
+        <v>2.85</v>
       </c>
       <c r="D130" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E130" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E130" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="4">
         <f t="shared" si="3"/>
         <v>258</v>
       </c>
       <c r="B131" s="4">
-        <f t="shared" ref="B131:B182" si="4">A131*PI()/180</f>
+        <f t="shared" ref="B131:B194" si="4">A131*PI()/180</f>
         <v>4.5029494701453698</v>
       </c>
       <c r="C131" s="4">
-        <v>3.51</v>
+        <v>2.82</v>
       </c>
       <c r="D131" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E131" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E131" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="4">
         <f t="shared" ref="A132:A180" si="5">A131+2</f>
         <v>260</v>
@@ -5311,18 +5439,18 @@
         <v>4.5378560551852569</v>
       </c>
       <c r="C132" s="4">
-        <v>3.48</v>
+        <v>2.79</v>
       </c>
       <c r="D132" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E132" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E132" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" s="4">
         <f t="shared" si="5"/>
         <v>262</v>
@@ -5332,18 +5460,18 @@
         <v>4.572762640225144</v>
       </c>
       <c r="C133" s="4">
-        <v>3.42</v>
+        <v>2.79</v>
       </c>
       <c r="D133" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E133" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E133" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
         <f t="shared" si="5"/>
         <v>264</v>
@@ -5353,18 +5481,18 @@
         <v>4.6076692252650302</v>
       </c>
       <c r="C134" s="4">
-        <v>3.39</v>
+        <v>2.77</v>
       </c>
       <c r="D134" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E134" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E134" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" s="4">
         <f t="shared" si="5"/>
         <v>266</v>
@@ -5374,18 +5502,18 @@
         <v>4.6425758103049164</v>
       </c>
       <c r="C135" s="4">
-        <v>3.38</v>
+        <v>2.75</v>
       </c>
       <c r="D135" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E135" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E135" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" s="4">
         <f t="shared" si="5"/>
         <v>268</v>
@@ -5395,18 +5523,18 @@
         <v>4.6774823953448026</v>
       </c>
       <c r="C136" s="4">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="D136" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E136" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E136" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" s="4">
         <f t="shared" si="5"/>
         <v>270</v>
@@ -5416,18 +5544,18 @@
         <v>4.7123889803846897</v>
       </c>
       <c r="C137" s="4">
-        <v>3.35</v>
+        <v>2.76</v>
       </c>
       <c r="D137" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E137" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E137" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" s="4">
         <f t="shared" si="5"/>
         <v>272</v>
@@ -5437,18 +5565,18 @@
         <v>4.7472955654245768</v>
       </c>
       <c r="C138" s="4">
-        <v>3.35</v>
+        <v>2.77</v>
       </c>
       <c r="D138" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E138" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E138" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" s="4">
         <f t="shared" si="5"/>
         <v>274</v>
@@ -5458,18 +5586,18 @@
         <v>4.782202150464463</v>
       </c>
       <c r="C139" s="4">
-        <v>3.37</v>
+        <v>2.79</v>
       </c>
       <c r="D139" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E139" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E139" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" s="4">
         <f t="shared" si="5"/>
         <v>276</v>
@@ -5479,18 +5607,19 @@
         <v>4.8171087355043491</v>
       </c>
       <c r="C140" s="4">
-        <v>3.37</v>
+        <v>2.81</v>
       </c>
       <c r="D140" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E140" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E140" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+      <c r="F140" s="6"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" s="4">
         <f t="shared" si="5"/>
         <v>278</v>
@@ -5500,18 +5629,19 @@
         <v>4.8520153205442362</v>
       </c>
       <c r="C141" s="4">
-        <v>3.41</v>
+        <v>2.86</v>
       </c>
       <c r="D141" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E141" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E141" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+      <c r="F141" s="6"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" s="4">
         <f t="shared" si="5"/>
         <v>280</v>
@@ -5521,18 +5651,18 @@
         <v>4.8869219055841224</v>
       </c>
       <c r="C142" s="4">
-        <v>3.45</v>
+        <v>2.87</v>
       </c>
       <c r="D142" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E142" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E142" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" s="4">
         <f t="shared" si="5"/>
         <v>282</v>
@@ -5542,18 +5672,18 @@
         <v>4.9218284906240086</v>
       </c>
       <c r="C143" s="4">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="D143" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E143" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E143" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="4">
         <f t="shared" si="5"/>
         <v>284</v>
@@ -5563,15 +5693,15 @@
         <v>4.9567350756638957</v>
       </c>
       <c r="C144" s="4">
-        <v>3.57</v>
+        <v>2.94</v>
       </c>
       <c r="D144" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E144" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E144" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
@@ -5584,15 +5714,15 @@
         <v>4.9916416607037828</v>
       </c>
       <c r="C145" s="4">
-        <v>3.63</v>
+        <v>2.98</v>
       </c>
       <c r="D145" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E145" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E145" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
@@ -5605,15 +5735,15 @@
         <v>5.026548245743669</v>
       </c>
       <c r="C146" s="4">
-        <v>3.7</v>
+        <v>3.01</v>
       </c>
       <c r="D146" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E146" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E146" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
@@ -5626,15 +5756,15 @@
         <v>5.0614548307835552</v>
       </c>
       <c r="C147" s="4">
-        <v>3.77</v>
+        <v>3.06</v>
       </c>
       <c r="D147" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E147" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E147" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
@@ -5647,15 +5777,15 @@
         <v>5.0963614158234423</v>
       </c>
       <c r="C148" s="4">
-        <v>3.84</v>
+        <v>3.13</v>
       </c>
       <c r="D148" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E148" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E148" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
@@ -5668,15 +5798,15 @@
         <v>5.1312680008633293</v>
       </c>
       <c r="C149" s="4">
-        <v>3.89</v>
+        <v>3.18</v>
       </c>
       <c r="D149" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E149" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E149" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
@@ -5689,15 +5819,15 @@
         <v>5.1661745859032155</v>
       </c>
       <c r="C150" s="4">
-        <v>4</v>
+        <v>3.24</v>
       </c>
       <c r="D150" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E150" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E150" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
@@ -5710,15 +5840,15 @@
         <v>5.2010811709431017</v>
       </c>
       <c r="C151" s="4">
-        <v>4.09</v>
+        <v>3.31</v>
       </c>
       <c r="D151" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E151" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E151" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
@@ -5731,15 +5861,15 @@
         <v>5.2359877559829888</v>
       </c>
       <c r="C152" s="4">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="D152" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E152" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E152" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
@@ -5752,15 +5882,15 @@
         <v>5.270894341022875</v>
       </c>
       <c r="C153" s="4">
-        <v>4.33</v>
+        <v>3.42</v>
       </c>
       <c r="D153" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E153" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E153" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
@@ -5773,15 +5903,15 @@
         <v>5.3058009260627612</v>
       </c>
       <c r="C154" s="4">
-        <v>4.4400000000000004</v>
+        <v>3.49</v>
       </c>
       <c r="D154" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E154" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E154" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
@@ -5794,15 +5924,15 @@
         <v>5.3407075111026483</v>
       </c>
       <c r="C155" s="4">
-        <v>4.4800000000000004</v>
+        <v>3.57</v>
       </c>
       <c r="D155" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E155" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E155" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
@@ -5815,15 +5945,15 @@
         <v>5.3756140961425354</v>
       </c>
       <c r="C156" s="4">
-        <v>4.5999999999999996</v>
+        <v>3.62</v>
       </c>
       <c r="D156" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E156" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E156" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
@@ -5836,15 +5966,15 @@
         <v>5.4105206811824216</v>
       </c>
       <c r="C157" s="4">
-        <v>4.71</v>
+        <v>3.69</v>
       </c>
       <c r="D157" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E157" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E157" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
@@ -5857,15 +5987,15 @@
         <v>5.4454272662223078</v>
       </c>
       <c r="C158" s="4">
-        <v>4.8</v>
+        <v>3.78</v>
       </c>
       <c r="D158" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E158" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E158" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
@@ -5878,15 +6008,15 @@
         <v>5.480333851262194</v>
       </c>
       <c r="C159" s="4">
-        <v>4.92</v>
+        <v>3.82</v>
       </c>
       <c r="D159" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E159" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E159" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
@@ -5899,15 +6029,15 @@
         <v>5.5152404363020811</v>
       </c>
       <c r="C160" s="4">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="D160" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E160" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E160" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
@@ -5920,15 +6050,15 @@
         <v>5.5501470213419681</v>
       </c>
       <c r="C161" s="4">
-        <v>5.1100000000000003</v>
+        <v>3.95</v>
       </c>
       <c r="D161" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E161" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E161" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
@@ -5941,15 +6071,15 @@
         <v>5.5850536063818543</v>
       </c>
       <c r="C162" s="4">
-        <v>5.24</v>
+        <v>3.99</v>
       </c>
       <c r="D162" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E162" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E162" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
@@ -5962,15 +6092,15 @@
         <v>5.6199601914217405</v>
       </c>
       <c r="C163" s="4">
-        <v>5.32</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="D163" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E163" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E163" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
@@ -5983,15 +6113,15 @@
         <v>5.6548667764616276</v>
       </c>
       <c r="C164" s="4">
-        <v>5.42</v>
+        <v>4.12</v>
       </c>
       <c r="D164" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E164" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E164" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
@@ -6004,15 +6134,15 @@
         <v>5.6897733615015138</v>
       </c>
       <c r="C165" s="4">
-        <v>5.53</v>
+        <v>4.21</v>
       </c>
       <c r="D165" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E165" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E165" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
@@ -6025,15 +6155,15 @@
         <v>5.7246799465414</v>
       </c>
       <c r="C166" s="4">
-        <v>5.62</v>
+        <v>4.26</v>
       </c>
       <c r="D166" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E166" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E166" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
@@ -6046,15 +6176,15 @@
         <v>5.7595865315812871</v>
       </c>
       <c r="C167" s="4">
-        <v>5.69</v>
+        <v>4.32</v>
       </c>
       <c r="D167" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E167" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E167" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
@@ -6067,15 +6197,15 @@
         <v>5.7944931166211742</v>
       </c>
       <c r="C168" s="4">
-        <v>5.78</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="D168" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E168" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E168" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
@@ -6088,15 +6218,15 @@
         <v>5.8293997016610613</v>
       </c>
       <c r="C169" s="4">
-        <v>5.83</v>
+        <v>4.41</v>
       </c>
       <c r="D169" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E169" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E169" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
@@ -6109,15 +6239,15 @@
         <v>5.8643062867009474</v>
       </c>
       <c r="C170" s="4">
-        <v>5.92</v>
+        <v>4.47</v>
       </c>
       <c r="D170" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E170" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E170" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
@@ -6130,15 +6260,15 @@
         <v>5.8992128717408336</v>
       </c>
       <c r="C171" s="4">
-        <v>5.97</v>
+        <v>4.49</v>
       </c>
       <c r="D171" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E171" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E171" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
@@ -6151,15 +6281,15 @@
         <v>5.9341194567807207</v>
       </c>
       <c r="C172" s="4">
-        <v>6.01</v>
+        <v>4.53</v>
       </c>
       <c r="D172" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E172" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E172" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
@@ -6172,15 +6302,15 @@
         <v>5.9690260418206069</v>
       </c>
       <c r="C173" s="4">
-        <v>6.09</v>
+        <v>4.58</v>
       </c>
       <c r="D173" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E173" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E173" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
@@ -6193,15 +6323,15 @@
         <v>6.0039326268604931</v>
       </c>
       <c r="C174" s="4">
-        <v>6.11</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="D174" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E174" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E174" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
@@ -6214,15 +6344,15 @@
         <v>6.0388392119003802</v>
       </c>
       <c r="C175" s="4">
-        <v>6.18</v>
+        <v>4.62</v>
       </c>
       <c r="D175" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E175" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E175" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
@@ -6235,15 +6365,15 @@
         <v>6.0737457969402664</v>
       </c>
       <c r="C176" s="4">
-        <v>6.22</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="D176" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E176" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E176" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
@@ -6256,15 +6386,15 @@
         <v>6.1086523819801526</v>
       </c>
       <c r="C177" s="4">
-        <v>6.28</v>
+        <v>4.66</v>
       </c>
       <c r="D177" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E177" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E177" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
@@ -6277,15 +6407,15 @@
         <v>6.1435589670200397</v>
       </c>
       <c r="C178" s="4">
-        <v>6.3</v>
+        <v>4.7</v>
       </c>
       <c r="D178" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E178" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E178" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
@@ -6298,15 +6428,15 @@
         <v>6.1784655520599268</v>
       </c>
       <c r="C179" s="4">
-        <v>6.35</v>
+        <v>4.7</v>
       </c>
       <c r="D179" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E179" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E179" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
@@ -6319,15 +6449,15 @@
         <v>6.2133721370998138</v>
       </c>
       <c r="C180" s="4">
-        <v>6.38</v>
+        <v>4.72</v>
       </c>
       <c r="D180" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E180" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E180" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
@@ -6340,20 +6470,20 @@
         <v>6.2482787221397</v>
       </c>
       <c r="C181" s="4">
-        <v>6.38</v>
+        <v>4.74</v>
       </c>
       <c r="D181" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E181" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E181" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="4">
-        <f t="shared" ref="A182" si="6">A181+2</f>
+        <f t="shared" ref="A182:A209" si="6">A181+2</f>
         <v>360</v>
       </c>
       <c r="B182" s="4">
@@ -6361,40 +6491,414 @@
         <v>6.2831853071795862</v>
       </c>
       <c r="C182" s="4">
-        <v>6.38</v>
+        <v>4.72</v>
       </c>
       <c r="D182" s="4">
         <f>Parametri!$A$4/SQRT(3)</f>
-        <v>5.0383315673172722E-3</v>
-      </c>
-      <c r="E182" s="4">
-        <f>Parametri!$B$2/SQRT(3)</f>
-        <v>3.333333511217112E-3</v>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E182" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A183" s="4">
+        <f t="shared" si="6"/>
+        <v>362</v>
+      </c>
+      <c r="B183" s="4">
+        <f t="shared" si="4"/>
+        <v>6.3180918922194724</v>
+      </c>
       <c r="C183" s="4">
-        <v>6.33</v>
+        <v>4.72</v>
+      </c>
+      <c r="D183" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E183" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A184" s="4">
+        <f t="shared" si="6"/>
+        <v>364</v>
+      </c>
+      <c r="B184" s="4">
+        <f t="shared" si="4"/>
+        <v>6.3529984772593595</v>
+      </c>
       <c r="C184" s="4">
-        <v>6.35</v>
+        <v>4.72</v>
+      </c>
+      <c r="D184" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E184" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A185" s="4">
+        <f t="shared" si="6"/>
+        <v>366</v>
+      </c>
+      <c r="B185" s="4">
+        <f t="shared" si="4"/>
+        <v>6.3879050622992457</v>
+      </c>
       <c r="C185" s="4">
-        <v>6.34</v>
+        <v>4.71</v>
+      </c>
+      <c r="D185" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E185" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A186" s="4">
+        <f t="shared" si="6"/>
+        <v>368</v>
+      </c>
+      <c r="B186" s="4">
+        <f t="shared" si="4"/>
+        <v>6.4228116473391319</v>
+      </c>
       <c r="C186" s="4">
-        <v>6.32</v>
+        <v>4.6900000000000004</v>
+      </c>
+      <c r="D186" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E186" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A187" s="4">
+        <f t="shared" si="6"/>
+        <v>370</v>
+      </c>
+      <c r="B187" s="4">
+        <f t="shared" si="4"/>
+        <v>6.457718232379019</v>
+      </c>
       <c r="C187" s="4">
-        <v>6.29</v>
+        <v>4.68</v>
+      </c>
+      <c r="D187" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E187" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A188" s="4">
+        <f t="shared" si="6"/>
+        <v>372</v>
+      </c>
+      <c r="B188" s="4">
+        <f t="shared" si="4"/>
+        <v>6.4926248174189052</v>
+      </c>
+      <c r="C188" s="4">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="D188" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E188" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A189" s="4">
+        <f t="shared" si="6"/>
+        <v>374</v>
+      </c>
+      <c r="B189" s="4">
+        <f t="shared" si="4"/>
+        <v>6.5275314024587932</v>
+      </c>
+      <c r="C189" s="4">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="D189" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E189" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A190" s="4">
+        <f t="shared" si="6"/>
+        <v>376</v>
+      </c>
+      <c r="B190" s="4">
+        <f t="shared" si="4"/>
+        <v>6.5624379874986793</v>
+      </c>
+      <c r="C190" s="4">
+        <v>4.58</v>
+      </c>
+      <c r="D190" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E190" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A191" s="4">
+        <f t="shared" si="6"/>
+        <v>378</v>
+      </c>
+      <c r="B191" s="4">
+        <f t="shared" si="4"/>
+        <v>6.5973445725385655</v>
+      </c>
+      <c r="C191" s="4">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="D191" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E191" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A192" s="4">
+        <f t="shared" si="6"/>
+        <v>380</v>
+      </c>
+      <c r="B192" s="4">
+        <f t="shared" si="4"/>
+        <v>6.6322511575784526</v>
+      </c>
+      <c r="C192" s="4">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="D192" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E192" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A193" s="4">
+        <f t="shared" si="6"/>
+        <v>382</v>
+      </c>
+      <c r="B193" s="4">
+        <f t="shared" si="4"/>
+        <v>6.6671577426183388</v>
+      </c>
+      <c r="C193" s="4">
+        <v>4.46</v>
+      </c>
+      <c r="D193" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E193" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A194" s="4">
+        <f t="shared" si="6"/>
+        <v>384</v>
+      </c>
+      <c r="B194" s="4">
+        <f t="shared" si="4"/>
+        <v>6.702064327658225</v>
+      </c>
+      <c r="C194" s="4">
+        <v>4.42</v>
+      </c>
+      <c r="D194" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E194" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A195" s="4">
+        <f t="shared" si="6"/>
+        <v>386</v>
+      </c>
+      <c r="B195" s="4">
+        <f t="shared" ref="B195:B202" si="7">A195*PI()/180</f>
+        <v>6.7369709126981121</v>
+      </c>
+      <c r="C195" s="4">
+        <v>4.37</v>
+      </c>
+      <c r="D195" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E195" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A196" s="4">
+        <f t="shared" si="6"/>
+        <v>388</v>
+      </c>
+      <c r="B196" s="4">
+        <f t="shared" si="7"/>
+        <v>6.7718774977379983</v>
+      </c>
+      <c r="C196" s="4">
+        <v>4.32</v>
+      </c>
+      <c r="D196" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E196" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A197" s="4">
+        <f t="shared" si="6"/>
+        <v>390</v>
+      </c>
+      <c r="B197" s="4">
+        <f t="shared" si="7"/>
+        <v>6.8067840827778845</v>
+      </c>
+      <c r="C197" s="4">
+        <v>4.26</v>
+      </c>
+      <c r="D197" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E197" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A198" s="4">
+        <f t="shared" si="6"/>
+        <v>392</v>
+      </c>
+      <c r="B198" s="4">
+        <f t="shared" si="7"/>
+        <v>6.8416906678177716</v>
+      </c>
+      <c r="C198" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="D198" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E198" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A199" s="4">
+        <f t="shared" si="6"/>
+        <v>394</v>
+      </c>
+      <c r="B199" s="4">
+        <f t="shared" si="7"/>
+        <v>6.8765972528576578</v>
+      </c>
+      <c r="C199" s="4">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="D199" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E199" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A200" s="4">
+        <f t="shared" si="6"/>
+        <v>396</v>
+      </c>
+      <c r="B200" s="4">
+        <f t="shared" si="7"/>
+        <v>6.9115038378975457</v>
+      </c>
+      <c r="C200" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D200" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E200" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A201" s="4">
+        <f t="shared" si="6"/>
+        <v>398</v>
+      </c>
+      <c r="B201" s="4">
+        <f t="shared" si="7"/>
+        <v>6.9464104229374319</v>
+      </c>
+      <c r="C201" s="4">
+        <v>4.05</v>
+      </c>
+      <c r="D201" s="4">
+        <f>Parametri!$A$4/SQRT(3)</f>
+        <v>1.0076663134634544E-2</v>
+      </c>
+      <c r="E201" s="8">
+        <f>Parametri!$B$2/SQRT(3)</f>
+        <v>1.1547005383792516E-2</v>
       </c>
     </row>
   </sheetData>
@@ -6613,15 +7117,15 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{052030C1-2942-4CC8-A44F-90DD685C420F}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="21343963-c43f-42a4-b0bc-b203e64410f4"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="21343963-c43f-42a4-b0bc-b203e64410f4"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
